--- a/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,69 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E7" s="2">
         <v>44561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44196</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>43830</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43465</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43100</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>42735</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42369</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42004</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41639</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41274</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>40908</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40543</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,8 +740,8 @@
       <c r="H8" s="3">
         <v>17800</v>
       </c>
-      <c r="I8" s="3">
-        <v>18300</v>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>5</v>
@@ -746,8 +749,8 @@
       <c r="K8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="3">
-        <v>20700</v>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M8" s="3">
         <v>20700</v>
@@ -758,9 +761,12 @@
       <c r="O8" s="3">
         <v>20700</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>20700</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,9 +1005,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,8 +1069,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1064,8 +1090,8 @@
       <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
-        <v>5400</v>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>5</v>
@@ -1073,8 +1099,8 @@
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="3">
-        <v>9200</v>
+      <c r="L17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M17" s="3">
         <v>9200</v>
@@ -1085,9 +1111,12 @@
       <c r="O17" s="3">
         <v>9200</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1106,8 +1135,8 @@
       <c r="H18" s="3">
         <v>16500</v>
       </c>
-      <c r="I18" s="3">
-        <v>12900</v>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
@@ -1115,8 +1144,8 @@
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="3">
-        <v>11400</v>
+      <c r="L18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M18" s="3">
         <v>11400</v>
@@ -1127,9 +1156,12 @@
       <c r="O18" s="3">
         <v>11400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>11400</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1178,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1166,8 +1199,8 @@
       <c r="H20" s="3">
         <v>-9200</v>
       </c>
-      <c r="I20" s="3">
-        <v>-7000</v>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
@@ -1175,8 +1208,8 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
-        <v>-7900</v>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M20" s="3">
         <v>-7900</v>
@@ -1187,20 +1220,23 @@
       <c r="O20" s="3">
         <v>-7900</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>21300</v>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E21" s="3">
-        <v>15400</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
+        <v>15300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>10700</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
@@ -1229,9 +1265,12 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,9 +1310,12 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1292,8 +1334,8 @@
       <c r="H23" s="3">
         <v>7400</v>
       </c>
-      <c r="I23" s="3">
-        <v>5900</v>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>5</v>
@@ -1301,8 +1343,8 @@
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="3">
-        <v>3500</v>
+      <c r="L23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M23" s="3">
         <v>3500</v>
@@ -1313,9 +1355,12 @@
       <c r="O23" s="3">
         <v>3500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1334,8 +1379,8 @@
       <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
-        <v>2400</v>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>5</v>
@@ -1343,8 +1388,8 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3">
-        <v>1500</v>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>1500</v>
@@ -1355,9 +1400,12 @@
       <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,9 +1445,12 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1418,8 +1469,8 @@
       <c r="H26" s="3">
         <v>4300</v>
       </c>
-      <c r="I26" s="3">
-        <v>3400</v>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>5</v>
@@ -1427,8 +1478,8 @@
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
-        <v>2100</v>
+      <c r="L26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M26" s="3">
         <v>2100</v>
@@ -1439,9 +1490,12 @@
       <c r="O26" s="3">
         <v>2100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1460,8 +1514,8 @@
       <c r="H27" s="3">
         <v>4100</v>
       </c>
-      <c r="I27" s="3">
-        <v>2900</v>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>5</v>
@@ -1469,8 +1523,8 @@
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
-        <v>1600</v>
+      <c r="L27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M27" s="3">
         <v>1600</v>
@@ -1481,9 +1535,12 @@
       <c r="O27" s="3">
         <v>1600</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,9 +1715,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1670,8 +1739,8 @@
       <c r="H32" s="3">
         <v>9200</v>
       </c>
-      <c r="I32" s="3">
-        <v>7000</v>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
@@ -1679,8 +1748,8 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
-        <v>7900</v>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M32" s="3">
         <v>7900</v>
@@ -1691,9 +1760,12 @@
       <c r="O32" s="3">
         <v>7900</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1712,8 +1784,8 @@
       <c r="H33" s="3">
         <v>4100</v>
       </c>
-      <c r="I33" s="3">
-        <v>2900</v>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>5</v>
@@ -1721,8 +1793,8 @@
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="3">
-        <v>1600</v>
+      <c r="L33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M33" s="3">
         <v>1600</v>
@@ -1733,9 +1805,12 @@
       <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,9 +1850,12 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1796,8 +1874,8 @@
       <c r="H35" s="3">
         <v>4100</v>
       </c>
-      <c r="I35" s="3">
-        <v>2900</v>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>5</v>
@@ -1805,8 +1883,8 @@
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L35" s="3">
-        <v>1600</v>
+      <c r="L35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M35" s="3">
         <v>1600</v>
@@ -1817,56 +1895,62 @@
       <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E38" s="2">
         <v>44561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44196</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>43830</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43465</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43100</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>42735</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42369</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42004</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41639</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41274</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>40908</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40543</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E41" s="3">
         <v>40700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E42" s="3">
         <v>4300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10600</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,9 +2253,12 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2194,51 +2298,57 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2278,9 +2388,12 @@
       <c r="O49" s="3">
         <v>4100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,9 +2478,12 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2404,9 +2523,12 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1113000</v>
+      </c>
+      <c r="E54" s="3">
         <v>958100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>865900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>696000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>622100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>610900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>513700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>513400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>459700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>454100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>444900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>387600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>347900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,50 +2654,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E57" s="3">
         <v>6600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2608,21 +2741,24 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2638,8 +2774,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -2650,9 +2786,12 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,9 +2831,12 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2708,7 +2850,7 @@
         <v>5900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2734,9 +2876,12 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2776,9 +2921,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1024500</v>
+      </c>
+      <c r="E66" s="3">
         <v>873800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>790200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>628600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>560600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>551200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>455100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>456000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>392100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>392400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>382000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>326600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>292600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3074,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>13700</v>
@@ -3086,11 +3253,14 @@
         <v>13700</v>
       </c>
       <c r="O70" s="3">
+        <v>13700</v>
+      </c>
+      <c r="P70" s="3">
         <v>8100</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>47600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>37500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>22800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E76" s="3">
         <v>84300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>75600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>67300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>61500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>59700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>58600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>57300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>53900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,56 +3570,62 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E80" s="2">
         <v>44561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44196</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>43830</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43465</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43100</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>42735</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42369</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42004</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41639</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41274</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>40908</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40543</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3450,8 +3644,8 @@
       <c r="H81" s="3">
         <v>4100</v>
       </c>
-      <c r="I81" s="3">
-        <v>2900</v>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>5</v>
@@ -3459,8 +3653,8 @@
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L81" s="3">
-        <v>1600</v>
+      <c r="L81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M81" s="3">
         <v>1600</v>
@@ -3471,9 +3665,12 @@
       <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,19 +3687,20 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>400</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
+      <c r="F83" s="3">
+        <v>400</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
@@ -3513,12 +3711,12 @@
       <c r="I83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3531,9 +3729,12 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,21 +3954,24 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>52000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3700</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3765,27 +3981,30 @@
       <c r="I89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>4500</v>
-      </c>
-      <c r="K89" s="3">
-        <v>6400</v>
       </c>
       <c r="L89" s="3">
         <v>6400</v>
       </c>
       <c r="M89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="N89" s="3">
         <v>8500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,19 +4021,20 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
+      <c r="F91" s="3">
+        <v>-100</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>5</v>
@@ -3825,27 +4045,30 @@
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1000</v>
       </c>
       <c r="L91" s="3">
         <v>-1000</v>
       </c>
       <c r="M91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,21 +4153,24 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-119500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-168700</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3951,12 +4180,12 @@
       <c r="I94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-56900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3969,9 +4198,12 @@
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,20 +4220,21 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -4012,26 +4245,29 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-2300</v>
       </c>
       <c r="L96" s="3">
         <v>-2300</v>
       </c>
       <c r="M96" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,21 +4397,24 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>77300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>157500</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4179,12 +4424,12 @@
       <c r="I100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>46700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4197,9 +4442,12 @@
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4224,8 +4472,8 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
@@ -4239,21 +4487,24 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3">
         <v>9900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G102" s="3" t="s">
         <v>5</v>
       </c>
@@ -4263,25 +4514,28 @@
       <c r="I102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
         <v>-5700</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-3900</v>
       </c>
       <c r="L102" s="3">
         <v>-3900</v>
       </c>
       <c r="M102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="N102" s="3">
         <v>11700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9500</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,104 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40543</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F8" s="3">
         <v>42000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>36400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>18600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>17900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>17800</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M8" s="3">
-        <v>20700</v>
+      <c r="M8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N8" s="3">
         <v>20700</v>
@@ -764,9 +767,12 @@
       <c r="P8" s="3">
         <v>20700</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>20700</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,9 +815,12 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,9 +979,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,9 +1027,12 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,40 +1095,41 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>-400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M17" s="3">
-        <v>9200</v>
+      <c r="M17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N17" s="3">
         <v>9200</v>
@@ -1114,41 +1140,44 @@
       <c r="P17" s="3">
         <v>9200</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>39900</v>
+      </c>
+      <c r="F18" s="3">
         <v>36300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>28200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>18300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>16500</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M18" s="3">
-        <v>11400</v>
+      <c r="M18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N18" s="3">
         <v>11400</v>
@@ -1159,9 +1188,12 @@
       <c r="P18" s="3">
         <v>11400</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>11400</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,40 +1211,41 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-15400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-13200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-8200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-9200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
-        <v>-7900</v>
+      <c r="M20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N20" s="3">
         <v>-7900</v>
@@ -1223,23 +1256,26 @@
       <c r="P20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>15700</v>
       </c>
       <c r="E21" s="3">
-        <v>15300</v>
+        <v>24300</v>
       </c>
       <c r="F21" s="3">
-        <v>10700</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
+        <v>21300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>15400</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>5</v>
@@ -1268,9 +1304,12 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1313,41 +1352,44 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F23" s="3">
         <v>20900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>14900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7400</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M23" s="3">
-        <v>3500</v>
+      <c r="M23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N23" s="3">
         <v>3500</v>
@@ -1358,41 +1400,44 @@
       <c r="P23" s="3">
         <v>3500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>4400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>4200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M24" s="3">
-        <v>1500</v>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N24" s="3">
         <v>1500</v>
@@ -1403,9 +1448,12 @@
       <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,41 +1496,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F26" s="3">
         <v>14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>10500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>4300</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M26" s="3">
-        <v>2100</v>
+      <c r="M26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N26" s="3">
         <v>2100</v>
@@ -1493,41 +1544,44 @@
       <c r="P26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F27" s="3">
         <v>14700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>10500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>4100</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M27" s="3">
-        <v>1600</v>
+      <c r="M27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N27" s="3">
         <v>1600</v>
@@ -1538,9 +1592,12 @@
       <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,41 +1784,44 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F32" s="3">
         <v>15400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>13200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>8200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>9200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
-        <v>7900</v>
+      <c r="M32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N32" s="3">
         <v>7900</v>
@@ -1763,41 +1832,44 @@
       <c r="P32" s="3">
         <v>7900</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>7900</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F33" s="3">
         <v>14700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>10500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>4100</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M33" s="3">
-        <v>1600</v>
+      <c r="M33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N33" s="3">
         <v>1600</v>
@@ -1808,9 +1880,12 @@
       <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,41 +1928,44 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F35" s="3">
         <v>14700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>10500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>4100</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M35" s="3">
-        <v>1600</v>
+      <c r="M35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N35" s="3">
         <v>1600</v>
@@ -1898,59 +1976,65 @@
       <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40543</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,98 +2072,105 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>75200</v>
+        <v>57800</v>
       </c>
       <c r="E41" s="3">
+        <v>77600</v>
+      </c>
+      <c r="F41" s="3">
         <v>40700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E42" s="3">
         <v>13600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10600</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2121,9 +2213,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2166,9 +2261,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2211,9 +2309,12 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2256,9 +2357,12 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2301,54 +2405,60 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L48" s="3">
         <v>5500</v>
       </c>
-      <c r="E48" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="M48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="O48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q48" s="3">
         <v>7300</v>
       </c>
-      <c r="G48" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>5800</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>5200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>6700</v>
-      </c>
-      <c r="P48" s="3">
-        <v>7300</v>
-      </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2391,9 +2501,12 @@
       <c r="P49" s="3">
         <v>4100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,9 +2597,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2526,9 +2645,12 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1113000</v>
+        <v>1122500</v>
       </c>
       <c r="E54" s="3">
+        <v>1115300</v>
+      </c>
+      <c r="F54" s="3">
         <v>958100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>865900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>696000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>622100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>610900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>513700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>513400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>459700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>454100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>444900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>387600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>347900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,53 +2784,57 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10200</v>
+        <v>4100</v>
       </c>
       <c r="E57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F57" s="3">
         <v>6600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2744,24 +2877,27 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2777,8 +2913,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -2789,9 +2925,12 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2834,9 +2973,12 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2853,7 +2995,7 @@
         <v>5900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2879,9 +3021,12 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2924,9 +3069,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1024500</v>
+        <v>1024800</v>
       </c>
       <c r="E66" s="3">
+        <v>1026800</v>
+      </c>
+      <c r="F66" s="3">
         <v>873800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>790200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>628600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>560600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>551200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>455100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>456000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>392100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>392400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>382000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>326600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>292600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3244,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>13700</v>
@@ -3256,11 +3423,14 @@
         <v>13700</v>
       </c>
       <c r="P70" s="3">
+        <v>13700</v>
+      </c>
+      <c r="Q70" s="3">
         <v>8100</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>69000</v>
       </c>
       <c r="E72" s="3">
+        <v>61400</v>
+      </c>
+      <c r="F72" s="3">
         <v>47600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>37500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>22800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E76" s="3">
         <v>88500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>84300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>75600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>67300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,91 +3761,97 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40543</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F81" s="3">
         <v>14700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>10500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>4100</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M81" s="3">
-        <v>1600</v>
+      <c r="M81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N81" s="3">
         <v>1600</v>
@@ -3668,9 +3862,12 @@
       <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,13 +3885,14 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
@@ -3702,8 +3900,8 @@
       <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+      <c r="G83" s="3">
+        <v>400</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
@@ -3714,12 +3912,12 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3732,9 +3930,12 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,24 +4170,27 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>-2400</v>
       </c>
       <c r="E89" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F89" s="3">
         <v>52000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3700</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3984,27 +4200,30 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>4500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>6400</v>
       </c>
       <c r="M89" s="3">
         <v>6400</v>
       </c>
       <c r="N89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="O89" s="3">
         <v>8500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,22 +4241,23 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
+      <c r="G91" s="3">
+        <v>-100</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>5</v>
@@ -4048,27 +4268,30 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1000</v>
       </c>
       <c r="M91" s="3">
         <v>-1000</v>
       </c>
       <c r="N91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,24 +4382,27 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>-20200</v>
       </c>
       <c r="E94" s="3">
+        <v>-117200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-119500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-168700</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4183,12 +4412,12 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-56900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4201,9 +4430,12 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,23 +4453,24 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="E96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F96" s="3">
         <v>-3000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -4248,26 +4481,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-2300</v>
       </c>
       <c r="M96" s="3">
         <v>-2300</v>
       </c>
       <c r="N96" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,24 +4642,27 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>2800</v>
       </c>
       <c r="E100" s="3">
+        <v>140300</v>
+      </c>
+      <c r="F100" s="3">
         <v>77300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>157500</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4427,12 +4672,12 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>46700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4445,9 +4690,12 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4475,8 +4723,8 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
@@ -4490,24 +4738,27 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>-19800</v>
       </c>
       <c r="E102" s="3">
+        <v>36900</v>
+      </c>
+      <c r="F102" s="3">
         <v>9900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7500</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>5</v>
       </c>
@@ -4517,25 +4768,28 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>-5700</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-3900</v>
       </c>
       <c r="M102" s="3">
         <v>-3900</v>
       </c>
       <c r="N102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="O102" s="3">
         <v>11700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -729,25 +729,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>60200</v>
+        <v>40300</v>
       </c>
       <c r="E8" s="3">
-        <v>49000</v>
+        <v>47400</v>
       </c>
       <c r="F8" s="3">
-        <v>42000</v>
+        <v>41200</v>
       </c>
       <c r="G8" s="3">
-        <v>36400</v>
+        <v>32600</v>
       </c>
       <c r="H8" s="3">
-        <v>18600</v>
+        <v>24900</v>
       </c>
       <c r="I8" s="3">
-        <v>17900</v>
+        <v>23400</v>
       </c>
       <c r="J8" s="3">
-        <v>17800</v>
+        <v>19800</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>5</v>
@@ -824,26 +824,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>47400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>41200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>32600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>23400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>19800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -988,26 +988,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1037,25 +1037,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1105,22 +1105,22 @@
         <v>25100</v>
       </c>
       <c r="E17" s="3">
-        <v>9100</v>
+        <v>23500</v>
       </c>
       <c r="F17" s="3">
-        <v>5700</v>
+        <v>20300</v>
       </c>
       <c r="G17" s="3">
-        <v>8300</v>
+        <v>17700</v>
       </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>16100</v>
       </c>
       <c r="I17" s="3">
-        <v>-400</v>
+        <v>15400</v>
       </c>
       <c r="J17" s="3">
-        <v>1300</v>
+        <v>13800</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1150,25 +1150,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>35100</v>
+        <v>15300</v>
       </c>
       <c r="E18" s="3">
-        <v>39900</v>
+        <v>23900</v>
       </c>
       <c r="F18" s="3">
-        <v>36300</v>
+        <v>20900</v>
       </c>
       <c r="G18" s="3">
-        <v>28200</v>
+        <v>14900</v>
       </c>
       <c r="H18" s="3">
-        <v>18400</v>
+        <v>8900</v>
       </c>
       <c r="I18" s="3">
-        <v>18300</v>
+        <v>8000</v>
       </c>
       <c r="J18" s="3">
-        <v>16500</v>
+        <v>5900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1217,26 +1217,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-19800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-15400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-9200</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1277,14 +1277,14 @@
       <c r="G21" s="3">
         <v>15400</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="H21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>6300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1313,26 +1313,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         <v>14900</v>
       </c>
       <c r="H23" s="3">
-        <v>10300</v>
+        <v>8900</v>
       </c>
       <c r="I23" s="3">
-        <v>9300</v>
+        <v>8000</v>
       </c>
       <c r="J23" s="3">
-        <v>7400</v>
+        <v>5900</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -1422,13 +1422,13 @@
         <v>4400</v>
       </c>
       <c r="H24" s="3">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="I24" s="3">
-        <v>3800</v>
+        <v>2200</v>
       </c>
       <c r="J24" s="3">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
@@ -1518,13 +1518,13 @@
         <v>10500</v>
       </c>
       <c r="H26" s="3">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="I26" s="3">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="J26" s="3">
-        <v>4300</v>
+        <v>3300</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -1566,13 +1566,13 @@
         <v>10500</v>
       </c>
       <c r="H27" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="I27" s="3">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="J27" s="3">
-        <v>4100</v>
+        <v>3300</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -1793,26 +1793,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>19800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>16000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>15400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>13200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>8200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>9200</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -1854,13 +1854,13 @@
         <v>10500</v>
       </c>
       <c r="H33" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="I33" s="3">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="J33" s="3">
-        <v>4100</v>
+        <v>3300</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -1950,13 +1950,13 @@
         <v>10500</v>
       </c>
       <c r="H35" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="I35" s="3">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="J35" s="3">
-        <v>4100</v>
+        <v>3300</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -2094,10 +2094,10 @@
         <v>38300</v>
       </c>
       <c r="I41" s="3">
-        <v>21700</v>
+        <v>11300</v>
       </c>
       <c r="J41" s="3">
-        <v>68800</v>
+        <v>62600</v>
       </c>
       <c r="K41" s="3">
         <v>24200</v>
@@ -2127,25 +2127,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>13900</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>13600</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>5300</v>
@@ -2174,26 +2174,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2222,26 +2222,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2271,25 +2271,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2319,25 +2319,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>81300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>34800</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>40200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>72800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2367,25 +2367,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>98500</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>97400</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>77200</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>71400</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>65600</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>81300</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>89800</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="E48" s="3">
         <v>6800</v>
@@ -2427,7 +2427,7 @@
         <v>7300</v>
       </c>
       <c r="H48" s="3">
-        <v>6300</v>
+        <v>7300</v>
       </c>
       <c r="I48" s="3">
         <v>5800</v>
@@ -2607,25 +2607,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>10400</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2791,25 +2791,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4100</v>
+        <v>1009700</v>
       </c>
       <c r="E57" s="3">
-        <v>11100</v>
+        <v>962700</v>
       </c>
       <c r="F57" s="3">
-        <v>6600</v>
+        <v>811600</v>
       </c>
       <c r="G57" s="3">
-        <v>3200</v>
+        <v>726300</v>
       </c>
       <c r="H57" s="3">
-        <v>3300</v>
+        <v>573800</v>
       </c>
       <c r="I57" s="3">
-        <v>2600</v>
+        <v>501200</v>
       </c>
       <c r="J57" s="3">
-        <v>2700</v>
+        <v>533500</v>
       </c>
       <c r="K57" s="3">
         <v>1900</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2854,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>56800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2886,17 +2886,17 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1300</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>5</v>
@@ -2935,25 +2935,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1014400</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>973800</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>815700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>726600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>574100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>558200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>548600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2983,19 +2983,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5900</v>
+        <v>6400</v>
       </c>
       <c r="E61" s="3">
-        <v>5900</v>
+        <v>48300</v>
       </c>
       <c r="F61" s="3">
-        <v>5900</v>
+        <v>55600</v>
       </c>
       <c r="G61" s="3">
-        <v>5900</v>
+        <v>60700</v>
       </c>
       <c r="H61" s="3">
-        <v>5900</v>
+        <v>51500</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -3031,25 +3031,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3494,14 +3494,14 @@
       <c r="G72" s="3">
         <v>37500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
+      <c r="H72" s="3">
+        <v>29900</v>
+      </c>
+      <c r="I72" s="3">
+        <v>26300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>23400</v>
       </c>
       <c r="K72" s="3">
         <v>22800</v>
@@ -3836,13 +3836,13 @@
         <v>10500</v>
       </c>
       <c r="H81" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="I81" s="3">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="J81" s="3">
-        <v>4100</v>
+        <v>3300</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -3903,14 +3903,14 @@
       <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
+      <c r="H83" s="3">
+        <v>500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -4186,19 +4186,19 @@
         <v>13700</v>
       </c>
       <c r="F89" s="3">
-        <v>52000</v>
+        <v>7500</v>
       </c>
       <c r="G89" s="3">
         <v>3700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
+      <c r="H89" s="3">
+        <v>24500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>4200</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -4259,14 +4259,14 @@
       <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
+      <c r="H91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-200</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
@@ -4398,19 +4398,19 @@
         <v>-117200</v>
       </c>
       <c r="F94" s="3">
-        <v>-119500</v>
+        <v>-75000</v>
       </c>
       <c r="G94" s="3">
         <v>-168700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
+      <c r="H94" s="3">
+        <v>-72300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-59600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-52400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -4460,25 +4460,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3300</v>
+        <v>3300</v>
       </c>
       <c r="E96" s="3">
-        <v>-3200</v>
+        <v>3200</v>
       </c>
       <c r="F96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2900</v>
+        <v>2900</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4661,16 +4661,16 @@
         <v>77300</v>
       </c>
       <c r="G100" s="3">
-        <v>157500</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
+        <v>157400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>64400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>92700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -4699,26 +4699,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4759,14 +4759,14 @@
       <c r="G102" s="3">
         <v>-7500</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
+      <c r="H102" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>44600</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,110 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40543</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E8" s="3">
         <v>40300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="3">
-        <v>20700</v>
+      <c r="N8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O8" s="3">
         <v>20700</v>
@@ -770,9 +773,12 @@
       <c r="Q8" s="3">
         <v>20700</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>20700</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,36 +824,39 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E10" s="3">
         <v>40300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,14 +998,17 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>4100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1009,8 +1028,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1030,9 +1049,12 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1049,16 +1071,16 @@
         <v>400</v>
       </c>
       <c r="H15" s="3">
+        <v>400</v>
+      </c>
+      <c r="I15" s="3">
         <v>500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,43 +1121,44 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E17" s="3">
         <v>25100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="3">
-        <v>9200</v>
+      <c r="N17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O17" s="3">
         <v>9200</v>
@@ -1143,44 +1169,47 @@
       <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>500</v>
+      </c>
+      <c r="E18" s="3">
         <v>15300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N18" s="3">
-        <v>11400</v>
+      <c r="N18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O18" s="3">
         <v>11400</v>
@@ -1191,9 +1220,12 @@
       <c r="Q18" s="3">
         <v>11400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>11400</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1247,8 +1280,8 @@
       <c r="M20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="3">
-        <v>-7900</v>
+      <c r="N20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O20" s="3">
         <v>-7900</v>
@@ -1259,36 +1292,39 @@
       <c r="Q20" s="3">
         <v>-7900</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>900</v>
+      </c>
+      <c r="E21" s="3">
         <v>15700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>21300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1307,9 +1343,12 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1334,8 +1373,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1355,44 +1394,47 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>15300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="3">
-        <v>3500</v>
+      <c r="N23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O23" s="3">
         <v>3500</v>
@@ -1403,44 +1445,47 @@
       <c r="Q23" s="3">
         <v>3500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2600</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="3">
-        <v>1500</v>
+      <c r="N24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O24" s="3">
         <v>1500</v>
@@ -1451,9 +1496,12 @@
       <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,44 +1547,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>10800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N26" s="3">
-        <v>2100</v>
+      <c r="N26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O26" s="3">
         <v>2100</v>
@@ -1547,44 +1598,47 @@
       <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>10800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N27" s="3">
-        <v>1600</v>
+      <c r="N27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O27" s="3">
         <v>1600</v>
@@ -1595,9 +1649,12 @@
       <c r="Q27" s="3">
         <v>1600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1823,8 +1892,8 @@
       <c r="M32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="3">
-        <v>7900</v>
+      <c r="N32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O32" s="3">
         <v>7900</v>
@@ -1835,44 +1904,47 @@
       <c r="Q32" s="3">
         <v>7900</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>10800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N33" s="3">
-        <v>1600</v>
+      <c r="N33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O33" s="3">
         <v>1600</v>
@@ -1883,9 +1955,12 @@
       <c r="Q33" s="3">
         <v>1600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,44 +2006,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>10800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N35" s="3">
-        <v>1600</v>
+      <c r="N35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O35" s="3">
         <v>1600</v>
@@ -1979,62 +2057,68 @@
       <c r="Q35" s="3">
         <v>1600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40543</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E41" s="3">
         <v>57800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>62600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2148,29 +2237,32 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>5300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2195,8 +2287,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2216,14 +2308,17 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>5100</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
@@ -2243,8 +2338,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2264,36 +2359,39 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3700</v>
+        <v>19300</v>
       </c>
       <c r="E45" s="3">
         <v>3700</v>
       </c>
       <c r="F45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G45" s="3">
         <v>2800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2312,36 +2410,39 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E46" s="3">
         <v>61500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>81300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>40200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>72800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2360,36 +2461,39 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E47" s="3">
         <v>98500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>97400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>77200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>71400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>81300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>89800</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2408,62 +2512,68 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>7300</v>
       </c>
       <c r="H48" s="3">
         <v>7300</v>
       </c>
       <c r="I48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J48" s="3">
         <v>5800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>4100</v>
@@ -2504,9 +2614,12 @@
       <c r="Q49" s="3">
         <v>4100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,36 +2716,39 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
         <v>10400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -2648,9 +2767,12 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1067600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1122500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1115300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>958100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>865900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>696000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>622100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>610900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>513700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>513400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>459700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>454100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>444900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>387600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>347900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,65 +2914,69 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1009700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>962700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>811600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>726300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>573800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>501200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>533500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -2854,14 +2987,14 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>56800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2880,9 +3013,12 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2916,8 +3052,8 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -2928,36 +3064,39 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>968800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1014400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>973800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>815700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>726600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>574100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>558200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>548600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2976,30 +3115,33 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E61" s="3">
         <v>6400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>55600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>60700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51500</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -3024,36 +3166,39 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3072,9 +3217,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>975300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1024800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1026800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>873800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>790200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>628600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>560600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>551200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>455100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>456000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>392100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>392400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>382000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>326600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>292600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3414,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>13700</v>
@@ -3426,11 +3593,14 @@
         <v>13700</v>
       </c>
       <c r="Q70" s="3">
+        <v>13700</v>
+      </c>
+      <c r="R70" s="3">
         <v>8100</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>69000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>61400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>37500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E76" s="3">
         <v>97700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>88500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>84300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>75600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>67300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,97 +3952,103 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40543</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>10800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N81" s="3">
-        <v>1600</v>
+      <c r="N81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O81" s="3">
         <v>1600</v>
@@ -3865,9 +4059,12 @@
       <c r="Q81" s="3">
         <v>1600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,13 +4083,14 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>400</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
@@ -3904,23 +4102,23 @@
         <v>400</v>
       </c>
       <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3933,9 +4131,12 @@
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>4500</v>
-      </c>
-      <c r="M89" s="3">
-        <v>6400</v>
       </c>
       <c r="N89" s="3">
         <v>6400</v>
       </c>
       <c r="O89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="P89" s="3">
         <v>8500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-200</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1000</v>
       </c>
       <c r="N91" s="3">
         <v>-1000</v>
       </c>
       <c r="O91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,42 +4611,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-117200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-75000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-168700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-72300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-52400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-56900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4433,9 +4662,12 @@
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,22 +4686,23 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>3300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>2900</v>
       </c>
       <c r="H96" s="3">
         <v>2900</v>
@@ -4478,32 +4711,35 @@
         <v>2900</v>
       </c>
       <c r="J96" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K96" s="3">
         <v>2800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-2300</v>
       </c>
       <c r="N96" s="3">
         <v>-2300</v>
       </c>
       <c r="O96" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,42 +4887,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>140300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>77300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>157400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>64400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>92700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>46700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4693,9 +4938,12 @@
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4720,14 +4968,14 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
@@ -4741,55 +4989,61 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>36900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>44600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
         <v>-5700</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-3900</v>
       </c>
       <c r="N102" s="3">
         <v>-3900</v>
       </c>
       <c r="O102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="P102" s="3">
         <v>11700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -732,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25800</v>
+        <v>25000</v>
       </c>
       <c r="E8" s="3">
         <v>40300</v>
@@ -834,7 +834,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>25800</v>
+        <v>25000</v>
       </c>
       <c r="E10" s="3">
         <v>40300</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>500</v>
+        <v>-300</v>
       </c>
       <c r="E18" s="3">
         <v>15300</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
         <v>15700</v>
@@ -1404,7 +1404,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3600</v>
+        <v>-4400</v>
       </c>
       <c r="E23" s="3">
         <v>15300</v>
@@ -1455,7 +1455,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
         <v>4500</v>
@@ -1557,7 +1557,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3700</v>
+        <v>-4200</v>
       </c>
       <c r="E26" s="3">
         <v>10800</v>
@@ -1608,7 +1608,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3700</v>
+        <v>-4200</v>
       </c>
       <c r="E27" s="3">
         <v>10800</v>
@@ -1914,7 +1914,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3700</v>
+        <v>-4200</v>
       </c>
       <c r="E33" s="3">
         <v>10800</v>
@@ -2016,7 +2016,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3700</v>
+        <v>-4200</v>
       </c>
       <c r="E35" s="3">
         <v>10800</v>
@@ -2318,7 +2318,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5100</v>
+        <v>4400</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
@@ -2369,7 +2369,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19300</v>
+        <v>3500</v>
       </c>
       <c r="E45" s="3">
         <v>3700</v>
@@ -2420,7 +2420,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>75800</v>
+        <v>59300</v>
       </c>
       <c r="E46" s="3">
         <v>61500</v>
@@ -2471,7 +2471,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>81600</v>
+        <v>81500</v>
       </c>
       <c r="E47" s="3">
         <v>98500</v>
@@ -2522,10 +2522,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5200</v>
+        <v>6400</v>
       </c>
       <c r="E48" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="F48" s="3">
         <v>6800</v>
@@ -2725,8 +2725,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>11200</v>
       </c>
       <c r="E52" s="3">
         <v>10400</v>
@@ -2828,7 +2828,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1067600</v>
+        <v>1067100</v>
       </c>
       <c r="E54" s="3">
         <v>1122500</v>
@@ -2972,10 +2972,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3074,10 +3074,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>968800</v>
+        <v>964700</v>
       </c>
       <c r="E60" s="3">
-        <v>1014400</v>
+        <v>1010300</v>
       </c>
       <c r="F60" s="3">
         <v>973800</v>
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5900</v>
+        <v>6800</v>
       </c>
       <c r="E61" s="3">
-        <v>6400</v>
+        <v>6900</v>
       </c>
       <c r="F61" s="3">
         <v>48300</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600</v>
+        <v>3900</v>
       </c>
       <c r="E62" s="3">
-        <v>4100</v>
+        <v>7600</v>
       </c>
       <c r="F62" s="3">
         <v>4700</v>
@@ -3380,7 +3380,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>975300</v>
+        <v>975400</v>
       </c>
       <c r="E66" s="3">
         <v>1024800</v>
@@ -3655,8 +3655,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>62900</v>
       </c>
       <c r="E72" s="3">
         <v>69000</v>
@@ -3860,7 +3860,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>92300</v>
+        <v>91700</v>
       </c>
       <c r="E76" s="3">
         <v>97700</v>
@@ -4018,7 +4018,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3700</v>
+        <v>-4200</v>
       </c>
       <c r="E81" s="3">
         <v>10800</v>
@@ -4089,8 +4089,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
@@ -4395,8 +4395,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>5900</v>
       </c>
       <c r="E89" s="3">
         <v>-2400</v>
@@ -4467,8 +4467,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
@@ -4620,8 +4620,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>36800</v>
       </c>
       <c r="E94" s="3">
         <v>-20200</v>
@@ -4693,7 +4693,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E96" s="3">
         <v>3300</v>
@@ -4896,8 +4896,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>-49000</v>
       </c>
       <c r="E100" s="3">
         <v>2800</v>
@@ -4999,7 +4999,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-6400</v>
       </c>
       <c r="E102" s="3">
         <v>-19800</v>

--- a/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,116 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40543</v>
       </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E8" s="3">
         <v>25000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19800</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
-        <v>20700</v>
+      <c r="O8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P8" s="3">
         <v>20700</v>
@@ -776,9 +779,12 @@
       <c r="R8" s="3">
         <v>20700</v>
       </c>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>20700</v>
+      </c>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -827,39 +833,42 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E10" s="3">
         <v>25000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>40300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -878,9 +887,12 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -900,8 +912,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -950,9 +963,12 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,18 +1017,21 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1031,8 +1050,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1052,9 +1071,12 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1074,16 +1096,16 @@
         <v>400</v>
       </c>
       <c r="I15" s="3">
+        <v>400</v>
+      </c>
+      <c r="J15" s="3">
         <v>500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1103,9 +1125,12 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,46 +1147,47 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E17" s="3">
         <v>25300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O17" s="3">
-        <v>9200</v>
+      <c r="O17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P17" s="3">
         <v>9200</v>
@@ -1172,47 +1198,50 @@
       <c r="R17" s="3">
         <v>9200</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O18" s="3">
-        <v>11400</v>
+      <c r="O18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P18" s="3">
         <v>11400</v>
@@ -1223,9 +1252,12 @@
       <c r="R18" s="3">
         <v>11400</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>11400</v>
+      </c>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1245,8 +1277,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1283,8 +1316,8 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
-        <v>-7900</v>
+      <c r="O20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P20" s="3">
         <v>-7900</v>
@@ -1295,39 +1328,42 @@
       <c r="R20" s="3">
         <v>-7900</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1346,9 +1382,12 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1376,8 +1415,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1397,47 +1436,50 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O23" s="3">
-        <v>3500</v>
+      <c r="O23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P23" s="3">
         <v>3500</v>
@@ -1448,47 +1490,50 @@
       <c r="R23" s="3">
         <v>3500</v>
       </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2600</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
-        <v>1500</v>
+      <c r="O24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P24" s="3">
         <v>1500</v>
@@ -1499,9 +1544,12 @@
       <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1550,47 +1598,50 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="3">
-        <v>2100</v>
+      <c r="O26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P26" s="3">
         <v>2100</v>
@@ -1601,47 +1652,50 @@
       <c r="R26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O27" s="3">
-        <v>1600</v>
+      <c r="O27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P27" s="3">
         <v>1600</v>
@@ -1652,9 +1706,12 @@
       <c r="R27" s="3">
         <v>1600</v>
       </c>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1703,9 +1760,12 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1754,9 +1814,12 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1805,9 +1868,12 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1856,9 +1922,12 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1895,8 +1964,8 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
-        <v>7900</v>
+      <c r="O32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P32" s="3">
         <v>7900</v>
@@ -1907,47 +1976,50 @@
       <c r="R32" s="3">
         <v>7900</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>7900</v>
+      </c>
+      <c r="T32" s="3"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="3">
-        <v>1600</v>
+      <c r="O33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P33" s="3">
         <v>1600</v>
@@ -1958,9 +2030,12 @@
       <c r="R33" s="3">
         <v>1600</v>
       </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2009,47 +2084,50 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="3">
-        <v>1600</v>
+      <c r="O35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P35" s="3">
         <v>1600</v>
@@ -2060,65 +2138,71 @@
       <c r="R35" s="3">
         <v>1600</v>
       </c>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T35" s="3"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40543</v>
       </c>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2138,8 +2222,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2159,59 +2244,63 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E41" s="3">
         <v>51400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>77600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>62600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4500</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3"/>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2240,29 +2329,32 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>5300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10600</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2290,8 +2382,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2311,18 +2403,21 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3"/>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E44" s="3">
         <v>4400</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2341,8 +2436,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2362,39 +2457,42 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3700</v>
       </c>
       <c r="F45" s="3">
         <v>3700</v>
       </c>
       <c r="G45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2413,39 +2511,42 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E46" s="3">
         <v>59300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>34800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>72800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2464,39 +2565,42 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3"/>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E47" s="3">
         <v>81500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>98500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>97400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>77200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>71400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>65600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>81300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>89800</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2515,60 +2619,66 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7300</v>
       </c>
       <c r="I48" s="3">
         <v>7300</v>
       </c>
       <c r="J48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7300</v>
       </c>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3"/>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2576,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>4100</v>
@@ -2617,9 +2727,12 @@
       <c r="R49" s="3">
         <v>4100</v>
       </c>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T49" s="3"/>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2668,9 +2781,12 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-      <c r="S50" s="3"/>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3"/>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2719,39 +2835,42 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3"/>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E52" s="3">
         <v>11200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -2770,9 +2889,12 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3"/>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2821,60 +2943,66 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1004600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1067100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1122500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1115300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>958100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>865900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>696000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>622100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>610900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>513700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>513400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>459700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>454100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>444900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>387600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>347900</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3"/>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2894,8 +3022,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2915,59 +3044,63 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>891100</v>
+      </c>
+      <c r="E57" s="3">
         <v>962600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1009700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>962700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>811600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>726300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>573800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>501200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>533500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3"/>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2990,14 +3123,14 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>56800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3016,9 +3149,12 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3"/>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3055,8 +3191,8 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3067,39 +3203,42 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>964700</v>
+        <v>891800</v>
       </c>
       <c r="E60" s="3">
+        <v>964200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1010300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>973800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>815700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>726600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>574100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>558200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>548600</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3118,33 +3257,36 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3"/>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6800</v>
+        <v>7100</v>
       </c>
       <c r="E61" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F61" s="3">
         <v>6900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>48300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>55600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>60700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3169,39 +3311,42 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3"/>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3220,9 +3365,12 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3"/>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3271,9 +3419,12 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3"/>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3322,9 +3473,12 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3373,60 +3527,66 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3"/>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>903400</v>
+      </c>
+      <c r="E66" s="3">
         <v>975400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1024800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1026800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>873800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>790200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>628600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>560600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>551200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>455100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>456000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>392100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>392400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>382000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>326600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>292600</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3446,8 +3606,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3496,9 +3657,12 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3547,9 +3711,12 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3"/>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3584,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>13700</v>
@@ -3596,11 +3763,14 @@
         <v>13700</v>
       </c>
       <c r="R70" s="3">
+        <v>13700</v>
+      </c>
+      <c r="S70" s="3">
         <v>8100</v>
       </c>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3"/>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3649,60 +3819,66 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-      <c r="S71" s="3"/>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3"/>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E72" s="3">
         <v>62900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>69000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>61400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>47600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>37500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10200</v>
       </c>
-      <c r="S72" s="3"/>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3"/>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3751,9 +3927,12 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-      <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3"/>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3802,9 +3981,12 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-      <c r="S74" s="3"/>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3"/>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3853,60 +4035,66 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3"/>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>101200</v>
+      </c>
+      <c r="E76" s="3">
         <v>91700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>97700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>84300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>75600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>67300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>61500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47200</v>
       </c>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3955,103 +4143,109 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3"/>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40543</v>
       </c>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2"/>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O81" s="3">
-        <v>1600</v>
+      <c r="O81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P81" s="3">
         <v>1600</v>
@@ -4062,9 +4256,12 @@
       <c r="R81" s="3">
         <v>1600</v>
       </c>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T81" s="3"/>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4084,8 +4281,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4105,23 +4303,23 @@
         <v>400</v>
       </c>
       <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4134,9 +4332,12 @@
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3"/>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4185,9 +4386,12 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3"/>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4236,9 +4440,12 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3"/>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4287,9 +4494,12 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3"/>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4338,9 +4548,12 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3"/>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4389,60 +4602,66 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3"/>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E89" s="3">
         <v>5900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>4500</v>
-      </c>
-      <c r="N89" s="3">
-        <v>6400</v>
       </c>
       <c r="O89" s="3">
         <v>6400</v>
       </c>
       <c r="P89" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Q89" s="3">
         <v>8500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6300</v>
       </c>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3"/>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4462,13 +4681,14 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
@@ -4477,44 +4697,47 @@
         <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1000</v>
       </c>
       <c r="O91" s="3">
         <v>-1000</v>
       </c>
       <c r="P91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3"/>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3"/>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4563,9 +4786,12 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3"/>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4614,45 +4840,48 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3"/>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E94" s="3">
         <v>36800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-117200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-75000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-168700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-72300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-59600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-52400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-56900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4665,9 +4894,12 @@
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3"/>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3"/>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4687,25 +4919,26 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>2900</v>
       </c>
       <c r="I96" s="3">
         <v>2900</v>
@@ -4714,32 +4947,35 @@
         <v>2900</v>
       </c>
       <c r="K96" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L96" s="3">
         <v>2800</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2400</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-2300</v>
       </c>
       <c r="O96" s="3">
         <v>-2300</v>
       </c>
       <c r="P96" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2100</v>
       </c>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3"/>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4788,9 +5024,12 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-      <c r="S97" s="3"/>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3"/>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4839,9 +5078,12 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-      <c r="S98" s="3"/>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3"/>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4890,45 +5132,48 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-      <c r="S99" s="3"/>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3"/>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-49000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>140300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>77300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>157400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>64400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>92700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>46700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4941,9 +5186,12 @@
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3"/>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3"/>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4971,14 +5219,14 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
@@ -4992,58 +5240,64 @@
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3"/>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3"/>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-49100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>44600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>-5700</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-3900</v>
       </c>
       <c r="O102" s="3">
         <v>-3900</v>
       </c>
       <c r="P102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="Q102" s="3">
         <v>11700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9500</v>
       </c>
-      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
